--- a/vlearn-app/public/quiz_excel/Day_14_AI Evaluation _ Benchmarking/Day_14_FULL_TOAN_BO_74_CAU.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_14_AI Evaluation _ Benchmarking/Day_14_FULL_TOAN_BO_74_CAU.xlsx
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1065,7 +1065,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Precision=Recall=3/4 nên F1=2PR/(P+R)=0,75.</t>
+          <t>Token F1: Multiset overlap = 3 tokens; candidate = 4 tokens, reference = 4 tokens. Precision = 3/4, Recall = 3/4 =&gt; F1 = 2 * (3/4 * 3/4) / (3/4 + 3/4) = 0,75.</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1265,7 +1265,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số là số từ của reference.</t>
+          <t>Word Error Rate (WER) = (S + D + I) / N_ref = (1 + 0 + 1) / 4 = 2 / 4 = 0,5.</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.708</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1463,7 +1463,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính precision tại từng rank relevant, lấy AP từng query rồi mới lấy mean.</t>
+          <t>Mean Average Precision (MAP): Query 1 relevant tại rank 1 và 3 =&gt; AP1 = (1/1 + 2/3) / 2 = (5/3) / 2 = 5/6 ≈ 0,8333. Query 2 relevant tại rank 2 và 3 =&gt; AP2 = (1/2 + 2/3) / 2 = (7/6) / 2 = 7/12 ≈ 0,5833. MAP = (5/6 + 7/12) / 2 = 17 / 24 ≈ 0,7083, làm tròn 3 chữ số là 0,708.</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
@@ -1518,7 +1518,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Thành phần nào không phụ thuộc detector hiện có?</t>
+          <t>Mẫu lấy vết (mixed trace sample) để vừa tìm lỗi chưa biết vừa phủ rủi ro đã biết gồm: (a) Lưu lượng ngẫu nhiên theo tỷ lệ cố định (để phát hiện lỗi chưa biết), (b) đại diện các nhóm truy vấn phổ biến, (c) các trường hợp bất thường và cờ cảnh báo tự động, (d) phản hồi tiêu cực từ người dùng.</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1806,7 +1806,7 @@
       <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Trừ chance agreement ở tử và chia cho dư địa còn lại.</t>
+          <t>Cohen's Kappa: κ = (p_o - p_e) / (1 - p_e) = (0,80 - 0,50) / (1 - 0,50) = 0,30 / 0,50 = 0,6.</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I28" s="4" t="n">
@@ -1909,7 +1909,7 @@
       <c r="J28" s="3" t="n"/>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mọi claim trong expected answer phải truy được về evidence nào?</t>
+          <t>Các trường bắt buộc để một ca kiểm thử trở thành golden record có thể kiểm toán: (a) Stable case ID bất biến, (b) câu hỏi và hành vi kỳ vọng được chuyên gia phê duyệt, (c) trích dẫn nguồn bằng chứng chính xác (provenance), (d) siêu dữ liệu về độ khó, mức độ rủi ro.</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I31" s="4" t="n">
@@ -2060,7 +2060,7 @@
       <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Evidence nào cho biết model đã nhìn thấy case và case đã đổi ra sao?</t>
+          <t>Các biện pháp kiểm soát benchmark đáng tin cậy: (a) Duy trì ID ổn định và lịch sử thay đổi, (b) tách biệt tập public/dev với tập private held-out (để chống overfitting), (c) ghi nhận truy cập và tăng version khi cập nhật, (d) đưa các lỗi production đã xác nhận vào tập living test qua quy trình phê duyệt.</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I33" s="4" t="n">
@@ -2169,7 +2169,7 @@
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Filter đánh chất lượng/evidence của candidate, không chỉ acceptance rate.</t>
+          <t>Lý do hợp lệ để loại bỏ một câu hỏi sinh tự động (synthetic candidate): (a) Đáp án kỳ vọng không có căn cứ từ nguồn tài liệu, (b) câu hỏi thiếu dữ kiện để có đáp án duy nhất, (c) trùng lặp ngữ nghĩa với ca kiểm thử đã có, (d) chỉ đổi tên riêng mà không thay đổi bản chất tác vụ.</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -2371,7 +2371,7 @@
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ đếm call thỏa đủ điều kiện redundant đã nêu.</t>
+          <t>Tỷ lệ redundant tool calls = (2 redundant calls / 8 total tool calls) * 100% = 25%.</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -2672,7 +2672,7 @@
       <c r="J43" s="3" t="n"/>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: ‘Tất cả k lần’ dùng p^k, không phải pass@k.</t>
+          <t>Xác suất pass^3 cho cả 3 run liên tiếp độc lập thành công với p=0,8: pass^3 = p^3 = 0,8^3 = 0,512 = 51,2%.</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -2720,7 +2720,7 @@
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dùng complement của việc cả ba lần đều fail.</t>
+          <t>Xác suất pass@3 (ít nhất một lần thành công trong 3 lần thử độc lập): pass@3 = 1 - (1 - p)^3 = 1 - (1 - 0,8)^3 = 1 - 0,2^3 = 1 - 0,008 = 0,992 = 99,2%.</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -3144,7 +3144,7 @@
       <c r="J52" s="3" t="n"/>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính update từ chênh lệch observed và expected.</t>
+          <t>Công thức Elo: R'_A = R_A + K * (observed - expected) = 1200 + 32 * (1 - 0,5) = 1200 + 16 = 1216.</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -3245,7 +3245,7 @@
       <c r="J54" s="3" t="n"/>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số là số cặp đã chạy đủ hai order.</t>
+          <t>Flip rate khi swap vị trí cặp câu trả lời A/B và B/A: (6 cặp đổi winner / 20 cặp đã thử) * 100% = 30%.</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -3389,7 +3389,7 @@
       <c r="J57" s="3" t="n"/>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số gồm toàn bộ case FAIL theo human gold.</t>
+          <t>True Positive Rate (TPR / Sensitivity / Recall) trên class FAIL: TP / (TP + FN) = 30 / (30 + 10) = 30 / 40 = 0,75 = 75%.</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -3437,7 +3437,7 @@
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính J rồi chia observed delta cho J.</t>
+          <t>Youden's J = TPR + TNR - 1 = 0,8 + 0,9 - 1 = 0,7. Công thức quan hệ observed delta ≈ J * true delta =&gt; true delta ≈ observed delta / J = 7 / 0,7 = 10 điểm phần trăm.</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -3783,7 +3783,7 @@
       <c r="J65" s="3" t="n"/>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ cộng hai ô hai version cho kết quả khác nhau.</t>
+          <t>Trong bảng 2x2 cho McNemar / exact-binomial test, số discordant pairs (cặp bất đồng) là tổng của hai ô chéo ngoài: b + c = 10 + 22 = 32.</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -4129,7 +4129,7 @@
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính từng cost component trước khi cộng.</t>
+          <t>Tổng direct evaluation cost: (500 checks * $0) + (200 judge calls * $0,02) + (20 human reviews * $2) = $0 + $4 + $40 = 44 USD.</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I73" s="4" t="n">
@@ -4184,7 +4184,7 @@
       <c r="J73" s="3" t="n"/>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một aggregate win có thể che regression nào?</t>
+          <t>Điều kiện cần thiết của một release gate có thể tái lập: (a) Khóa phiên bản baseline và bộ test suite, (b) so sánh chênh lệch metric trên cùng tập ca kiểm thử (paired delta), (c) đặt ngưỡng bắt buộc cho các phân khúc trọng yếu (critical slice) và an toàn, (d) có quy tắc rõ ràng xử lý độ không chắc chắn.</t>
         </is>
       </c>
     </row>
